--- a/ShiftCipher/673380289_4_Testcase_template.xlsx
+++ b/ShiftCipher/673380289_4_Testcase_template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="102">
   <si>
     <t>Use case ID/ Req. ID</t>
   </si>
@@ -211,10 +211,37 @@
     <t>VRIWZDUH</t>
   </si>
   <si>
+    <t>message = "software"</t>
+  </si>
+  <si>
     <t>2. message เป็นตัวอักษร a-z จะให้ผลลัพธ์เป็น a-z</t>
   </si>
   <si>
-    <t>2. key = 3</t>
+    <t>message = "EFgh"</t>
+  </si>
+  <si>
+    <t>3. message เป็นตัวอักษรใหญ่และตัวอักษรเล็กปนกัน จะให้ผลลัพธ์ เป็น A-Z, a-z</t>
+  </si>
+  <si>
+    <t>เมธอด return ผลลัพธ์เป็น "HIJK"</t>
+  </si>
+  <si>
+    <t>HIJK</t>
+  </si>
+  <si>
+    <t>message = "ABC123"</t>
+  </si>
+  <si>
+    <t>4. message เป็นตัวอักษรใหญ่และตัวเลขปนกัน จะให้ผลลัพธ์ เป็น A-Z, 0-9 โดยที่ตัวเลขคงเดิม</t>
+  </si>
+  <si>
+    <t>เมธอด return ผลลัพธ์เป็น "DEF123"</t>
+  </si>
+  <si>
+    <t>DEF123</t>
+  </si>
+  <si>
+    <t>5. key = 3</t>
   </si>
   <si>
     <t>Alternate flows:</t>
@@ -295,16 +322,10 @@
     <t>เมธอด จะแปลงข้อความเป็นตัวพิมพ์ใหญ่(EFGH) ก่อนแล้ว return ผลลัพธ์เป็น "HIJK"</t>
   </si>
   <si>
-    <t>เมธอด return ผลลัพธ์เป็น "HIJK"</t>
-  </si>
-  <si>
     <t>TC04</t>
   </si>
   <si>
     <t>ABC123</t>
-  </si>
-  <si>
-    <t>เมธอด return ผลลัพธ์เป็น "DEF123"</t>
   </si>
 </sst>
 </file>
@@ -314,7 +335,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -360,6 +381,12 @@
       <sz val="18.0"/>
       <color theme="1"/>
       <name val="TH Sarabun PSK"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -491,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -584,7 +611,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
@@ -593,14 +620,26 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -643,7 +682,7 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -30036,7 +30075,7 @@
     <col customWidth="1" min="1" max="1" width="24.43"/>
     <col customWidth="1" min="2" max="2" width="139.57"/>
     <col customWidth="1" min="3" max="3" width="37.29"/>
-    <col customWidth="1" min="4" max="4" width="29.0"/>
+    <col customWidth="1" min="4" max="4" width="78.43"/>
     <col customWidth="1" min="5" max="5" width="52.0"/>
     <col customWidth="1" min="6" max="6" width="28.29"/>
     <col customWidth="1" min="7" max="7" width="25.86"/>
@@ -30188,13 +30227,13 @@
     <row r="10">
       <c r="A10" s="39"/>
       <c r="B10" s="39"/>
-      <c r="C10" s="38" t="s">
-        <v>46</v>
+      <c r="C10" s="40" t="s">
+        <v>63</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="41"/>
       <c r="F10" s="37" t="s">
         <v>62</v>
       </c>
@@ -30204,32 +30243,54 @@
       <c r="H10" s="38"/>
     </row>
     <row r="11">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38" t="s">
-        <v>64</v>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="37" t="s">
+        <v>65</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="D11" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>4</v>
+      </c>
       <c r="H11" s="38"/>
     </row>
     <row r="12">
       <c r="A12" s="38"/>
       <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="C12" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>4</v>
+      </c>
       <c r="H12" s="38"/>
     </row>
     <row r="13">
       <c r="A13" s="38"/>
       <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
+      <c r="C13" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
@@ -30276,22 +30337,22 @@
       <c r="H17" s="38"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="s">
-        <v>65</v>
+      <c r="A18" s="45" t="s">
+        <v>74</v>
       </c>
-      <c r="B18" s="42" t="s">
-        <v>66</v>
+      <c r="B18" s="46" t="s">
+        <v>75</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -31277,8 +31338,8 @@
   <mergeCells count="11">
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="E9:E11"/>
     <mergeCell ref="B18:E18"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -31340,8 +31401,8 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="44" t="s">
-        <v>67</v>
+      <c r="A2" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -31349,25 +31410,25 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
     </row>
     <row r="3" ht="24.0" customHeight="1">
       <c r="A3" s="1"/>
@@ -31398,16 +31459,16 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" ht="24.0" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>68</v>
+      <c r="A4" s="50" t="s">
+        <v>77</v>
       </c>
-      <c r="B4" s="47" t="s">
-        <v>69</v>
+      <c r="B4" s="51" t="s">
+        <v>78</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="46" t="s">
-        <v>70</v>
+      <c r="E4" s="50" t="s">
+        <v>79</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>34</v>
@@ -31434,19 +31495,19 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" ht="24.0" customHeight="1">
-      <c r="A5" s="46" t="s">
-        <v>71</v>
+      <c r="A5" s="50" t="s">
+        <v>80</v>
       </c>
-      <c r="B5" s="47" t="s">
-        <v>72</v>
+      <c r="B5" s="51" t="s">
+        <v>81</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="46" t="s">
-        <v>73</v>
+      <c r="E5" s="50" t="s">
+        <v>82</v>
       </c>
-      <c r="F5" s="48" t="s">
-        <v>74</v>
+      <c r="F5" s="52" t="s">
+        <v>83</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1"/>
@@ -31470,11 +31531,11 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
-      <c r="A6" s="49" t="s">
-        <v>75</v>
+      <c r="A6" s="53" t="s">
+        <v>84</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>76</v>
+      <c r="B6" s="54" t="s">
+        <v>85</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -31530,86 +31591,86 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" ht="24.0" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="51" t="s">
-        <v>77</v>
+      <c r="B8" s="55" t="s">
+        <v>86</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="56" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="51" t="s">
-        <v>78</v>
+      <c r="E8" s="55" t="s">
+        <v>87</v>
       </c>
-      <c r="F8" s="51" t="s">
-        <v>79</v>
+      <c r="F8" s="55" t="s">
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="53"/>
-      <c r="T8" s="53"/>
-      <c r="U8" s="53"/>
-      <c r="V8" s="53"/>
-      <c r="W8" s="53"/>
-      <c r="X8" s="53"/>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="53"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
     </row>
     <row r="9" ht="24.0" customHeight="1">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="54" t="s">
-        <v>81</v>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="58" t="s">
+        <v>90</v>
       </c>
-      <c r="D9" s="54" t="s">
-        <v>82</v>
+      <c r="D9" s="58" t="s">
+        <v>91</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="53"/>
-      <c r="T9" s="53"/>
-      <c r="U9" s="53"/>
-      <c r="V9" s="53"/>
-      <c r="W9" s="53"/>
-      <c r="X9" s="53"/>
-      <c r="Y9" s="53"/>
-      <c r="Z9" s="53"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="57"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
     </row>
     <row r="10" ht="24.0" customHeight="1">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="60" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D10" s="9">
         <v>3.0</v>
@@ -31617,10 +31678,10 @@
       <c r="E10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="57" t="s">
+      <c r="G10" s="61" t="s">
         <v>4</v>
       </c>
       <c r="H10" s="1"/>
@@ -31646,21 +31707,21 @@
     <row r="11" ht="24.0" customHeight="1">
       <c r="A11" s="39"/>
       <c r="B11" s="9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D11" s="9">
         <v>3.0</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="57" t="s">
+      <c r="G11" s="61" t="s">
         <v>4</v>
       </c>
       <c r="H11" s="1"/>
@@ -31686,21 +31747,21 @@
     <row r="12" ht="24.0" customHeight="1">
       <c r="A12" s="39"/>
       <c r="B12" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D12" s="13">
         <v>3.0</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
-      <c r="F12" s="57" t="s">
-        <v>91</v>
+      <c r="F12" s="61" t="s">
+        <v>67</v>
       </c>
-      <c r="G12" s="57" t="s">
+      <c r="G12" s="61" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="1"/>
@@ -31724,23 +31785,23 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" ht="24.0" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D13" s="13">
         <v>3.0</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
-      <c r="F13" s="57" t="s">
-        <v>94</v>
+      <c r="F13" s="61" t="s">
+        <v>71</v>
       </c>
-      <c r="G13" s="57" t="s">
+      <c r="G13" s="61" t="s">
         <v>4</v>
       </c>
       <c r="H13" s="1"/>
